--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -1,27 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenSource\GF_X\AAAGameData\DataTables\Core\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120"/>
+    <workbookView windowWidth="29868" windowHeight="14855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
   <si>
     <t>#</t>
   </si>
@@ -41,6 +49,9 @@
     <t>PauseCoveredUI</t>
   </si>
   <si>
+    <t>UIGroupId</t>
+  </si>
+  <si>
     <t>EscapeClose</t>
   </si>
   <si>
@@ -53,116 +64,14 @@
     <t>bool</t>
   </si>
   <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>游戏界面</t>
-  </si>
-  <si>
-    <t>GameUIForm</t>
-  </si>
-  <si>
-    <t>SettingDialog</t>
-  </si>
-  <si>
-    <t>CommonDialog</t>
-  </si>
-  <si>
-    <t>ToastTips</t>
-  </si>
-  <si>
-    <t>GameOverUIForm</t>
-  </si>
-  <si>
-    <t>MenuUIForm</t>
-  </si>
-  <si>
-    <t>返回键触发关闭界面</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>LanguagesDialog</t>
-  </si>
-  <si>
-    <t>RatingDialog</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TermsOfServiceDialog</t>
-  </si>
-  <si>
-    <t>同组界面被覆盖时是否隐藏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Topbar</t>
-  </si>
-  <si>
-    <t>主菜单</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>游戏结算</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>顶部资源栏</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>评分</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>服务条款</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>通用提示对话框</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语言设置</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>吐司提示</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>提示(顶层)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话框(中层)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>主界面(顶层)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>显示顺序,相对于Group,每个Group间隔100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>UIGroupId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>i</t>
     </r>
     <r>
@@ -170,24 +79,108 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="宋体"/>
-        <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
       <t>nt</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>显示顺序,相对于Group,每个Group间隔100</t>
+  </si>
+  <si>
+    <t>同组界面被覆盖时是否隐藏</t>
   </si>
   <si>
     <t>UI组Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>返回键触发关闭界面</t>
+  </si>
+  <si>
+    <t>主界面(顶层)</t>
+  </si>
+  <si>
+    <t>主菜单</t>
+  </si>
+  <si>
+    <t>StartMenuUI</t>
+  </si>
+  <si>
+    <t>游戏界面</t>
+  </si>
+  <si>
+    <t>GameUIForm</t>
+  </si>
+  <si>
+    <t>游戏结算</t>
+  </si>
+  <si>
+    <t>GameOverUIForm</t>
+  </si>
+  <si>
+    <t>顶部资源栏</t>
+  </si>
+  <si>
+    <t>Topbar</t>
+  </si>
+  <si>
+    <t>对话框(中层)</t>
+  </si>
+  <si>
+    <t>设置</t>
+  </si>
+  <si>
+    <t>SettingDialog</t>
+  </si>
+  <si>
+    <t>评分</t>
+  </si>
+  <si>
+    <t>RatingDialog</t>
+  </si>
+  <si>
+    <t>服务条款</t>
+  </si>
+  <si>
+    <t>TermsOfServiceDialog</t>
+  </si>
+  <si>
+    <t>通用提示对话框</t>
+  </si>
+  <si>
+    <t>CommonDialog</t>
+  </si>
+  <si>
+    <t>语言设置</t>
+  </si>
+  <si>
+    <t>LanguagesDialog</t>
+  </si>
+  <si>
+    <t>提示(顶层)</t>
+  </si>
+  <si>
+    <t>吐司提示</t>
+  </si>
+  <si>
+    <t>ToastTips</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,29 +189,345 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -226,25 +535,311 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -293,7 +888,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -328,7 +923,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -531,25 +1126,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.1296296296296" customWidth="1"/>
+    <col min="3" max="3" width="15.1296296296296" customWidth="1"/>
+    <col min="4" max="4" width="40.1296296296296" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
-    <col min="6" max="6" width="25.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.5" customWidth="1"/>
+    <col min="7" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -557,7 +1152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -574,78 +1169,78 @@
         <v>5</v>
       </c>
       <c r="G2" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="H2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:8">
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -657,18 +1252,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:8">
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -680,18 +1275,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:8">
       <c r="B8">
         <v>3</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -703,18 +1298,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:8">
       <c r="B9">
         <v>4</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" t="b">
         <v>0</v>
@@ -726,17 +1321,17 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1"/>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:8">
       <c r="B11">
         <v>5</v>
       </c>
@@ -747,7 +1342,7 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -759,18 +1354,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:8">
       <c r="B12">
         <v>6</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -782,18 +1377,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:8">
       <c r="B13">
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -805,18 +1400,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:8">
       <c r="B14">
         <v>8</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>3</v>
       </c>
       <c r="E14" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -828,18 +1423,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:8">
       <c r="B15">
         <v>9</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F15" t="b">
         <v>0</v>
@@ -851,27 +1446,27 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17">
         <v>10</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D17">
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F17" t="b">
         <v>0</v>
@@ -884,28 +1479,30 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
   <si>
     <t>#</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>ToastTips</t>
+  </si>
+  <si>
+    <t>云存档界面</t>
+  </si>
+  <si>
+    <t>CloudArchiveUI</t>
   </si>
 </sst>
 </file>
@@ -1132,7 +1138,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.1296296296296" customWidth="1"/>
@@ -1476,6 +1482,29 @@
       </c>
       <c r="H17" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>41</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="44">
   <si>
     <t>#</t>
   </si>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <t>CloudArchiveUI</t>
+  </si>
+  <si>
+    <t>新游戏界面</t>
+  </si>
+  <si>
+    <t>NewGameUI</t>
   </si>
 </sst>
 </file>
@@ -1138,7 +1144,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.1296296296296" customWidth="1"/>
@@ -1504,6 +1510,29 @@
         <v>2</v>
       </c>
       <c r="H18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19">
+        <v>12</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19">
+        <v>9</v>
+      </c>
+      <c r="E19" t="s">
+        <v>43</v>
+      </c>
+      <c r="F19" t="b">
+        <v>0</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
         <v>1</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
   <si>
     <t>#</t>
   </si>
@@ -264,6 +264,12 @@
   </si>
   <si>
     <t>EscapeResultUI</t>
+  </si>
+  <si>
+    <t>仓库界面</t>
+  </si>
+  <si>
+    <t>WarehouseUI</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1234,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.1333333333333" customWidth="1"/>
@@ -1940,6 +1946,29 @@
       </c>
       <c r="H33" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34">
+        <v>29</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
   <si>
     <t>#</t>
   </si>
@@ -270,6 +270,12 @@
   </si>
   <si>
     <t>WarehouseUI</t>
+  </si>
+  <si>
+    <t>图鉴界面</t>
+  </si>
+  <si>
+    <t>DictionariesUI</t>
   </si>
 </sst>
 </file>
@@ -1234,7 +1240,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.1333333333333" customWidth="1"/>
@@ -1968,6 +1974,29 @@
         <v>1</v>
       </c>
       <c r="H34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35">
+        <v>30</v>
+      </c>
+      <c r="C35" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35">
+        <v>2</v>
+      </c>
+      <c r="E35" t="s">
+        <v>75</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>1</v>
+      </c>
+      <c r="H35" t="b">
         <v>1</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="78">
   <si>
     <t>#</t>
   </si>
@@ -276,6 +276,12 @@
   </si>
   <si>
     <t>DictionariesUI</t>
+  </si>
+  <si>
+    <t>出战预设界面</t>
+  </si>
+  <si>
+    <t>BattlePresetUI</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1246,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.1333333333333" customWidth="1"/>
@@ -1997,6 +2003,29 @@
         <v>1</v>
       </c>
       <c r="H35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36">
+        <v>31</v>
+      </c>
+      <c r="C36" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36">
+        <v>2</v>
+      </c>
+      <c r="E36" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36">
+        <v>1</v>
+      </c>
+      <c r="H36" t="b">
         <v>1</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="27948" windowHeight="11855"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
   <si>
     <t>#</t>
   </si>
@@ -110,24 +110,6 @@
     <t>StartMenuUI</t>
   </si>
   <si>
-    <t>游戏界面</t>
-  </si>
-  <si>
-    <t>GameUIForm</t>
-  </si>
-  <si>
-    <t>游戏结算</t>
-  </si>
-  <si>
-    <t>GameOverUIForm</t>
-  </si>
-  <si>
-    <t>顶部资源栏</t>
-  </si>
-  <si>
-    <t>Topbar</t>
-  </si>
-  <si>
     <t>对话框(中层)</t>
   </si>
   <si>
@@ -135,30 +117,6 @@
   </si>
   <si>
     <t>SettingDialog</t>
-  </si>
-  <si>
-    <t>评分</t>
-  </si>
-  <si>
-    <t>RatingDialog</t>
-  </si>
-  <si>
-    <t>服务条款</t>
-  </si>
-  <si>
-    <t>TermsOfServiceDialog</t>
-  </si>
-  <si>
-    <t>通用提示对话框</t>
-  </si>
-  <si>
-    <t>CommonDialog</t>
-  </si>
-  <si>
-    <t>语言设置</t>
-  </si>
-  <si>
-    <t>LanguagesDialog</t>
   </si>
   <si>
     <t>提示(顶层)</t>
@@ -1246,12 +1204,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:H29"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="13.1333333333333" customWidth="1"/>
-    <col min="3" max="3" width="25.4416666666667" customWidth="1"/>
-    <col min="4" max="4" width="40.1333333333333" customWidth="1"/>
+    <col min="2" max="2" width="13.1296296296296" customWidth="1"/>
+    <col min="3" max="3" width="25.4444444444444" customWidth="1"/>
+    <col min="4" max="4" width="40.1296296296296" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
@@ -1367,99 +1325,85 @@
       </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="A7" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="b">
-        <v>0</v>
-      </c>
+      <c r="C7" s="1"/>
+      <c r="E7" s="1"/>
     </row>
     <row r="8" spans="1:8">
       <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="b">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10">
+        <v>10</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10">
         <v>3</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
       <c r="B11">
-        <v>5</v>
-      </c>
-      <c r="C11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
         <v>27</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>28</v>
-      </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1470,22 +1414,22 @@
     </row>
     <row r="12" spans="1:8">
       <c r="B12">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>30</v>
+      <c r="E12" t="s">
+        <v>29</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
@@ -1493,19 +1437,19 @@
     </row>
     <row r="13" spans="1:8">
       <c r="B13">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>31</v>
+        <v>13</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
       </c>
       <c r="D13">
         <v>2</v>
       </c>
       <c r="E13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1516,22 +1460,22 @@
     </row>
     <row r="14" spans="1:8">
       <c r="B14">
-        <v>8</v>
-      </c>
-      <c r="C14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
         <v>33</v>
       </c>
-      <c r="D14">
+      <c r="F14" t="b">
+        <v>0</v>
+      </c>
+      <c r="G14">
         <v>3</v>
-      </c>
-      <c r="E14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
       </c>
       <c r="H14" t="b">
         <v>0</v>
@@ -1539,41 +1483,55 @@
     </row>
     <row r="15" spans="1:8">
       <c r="B15">
-        <v>9</v>
-      </c>
-      <c r="C15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
         <v>35</v>
       </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="B16">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
         <v>36</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>2</v>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" s="1" t="s">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="1"/>
-    </row>
-    <row r="17" spans="2:8">
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" spans="2:8">
       <c r="B17">
-        <v>10</v>
-      </c>
-      <c r="C17" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
         <v>38</v>
       </c>
       <c r="D17">
@@ -1586,15 +1544,15 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H17" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" customFormat="1" spans="2:8">
       <c r="B18">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
         <v>40</v>
@@ -1609,21 +1567,21 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" spans="2:8">
       <c r="B19">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E19" t="s">
         <v>43</v>
@@ -1635,12 +1593,12 @@
         <v>1</v>
       </c>
       <c r="H19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="2:8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" spans="2:8">
       <c r="B20">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
         <v>44</v>
@@ -1655,21 +1613,21 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:8">
       <c r="B21">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
         <v>46</v>
       </c>
       <c r="D21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="s">
         <v>47</v>
@@ -1678,7 +1636,7 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H21" t="b">
         <v>0</v>
@@ -1686,7 +1644,7 @@
     </row>
     <row r="22" spans="2:8">
       <c r="B22">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C22" t="s">
         <v>48</v>
@@ -1709,13 +1667,13 @@
     </row>
     <row r="23" spans="2:8">
       <c r="B23">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
         <v>50</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="s">
         <v>51</v>
@@ -1727,24 +1685,24 @@
         <v>1</v>
       </c>
       <c r="H23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customFormat="1" spans="2:8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8">
       <c r="B24">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
         <v>52</v>
       </c>
       <c r="D24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E24" t="s">
         <v>53</v>
       </c>
       <c r="F24" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1753,21 +1711,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="1" spans="2:8">
+    <row r="25" spans="2:8">
       <c r="B25">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C25" t="s">
         <v>54</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" t="s">
         <v>55</v>
       </c>
       <c r="F25" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -1778,30 +1736,30 @@
     </row>
     <row r="26" customFormat="1" spans="2:8">
       <c r="B26">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C26" t="s">
         <v>56</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="s">
         <v>57</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="1" spans="2:8">
+    <row r="27" spans="2:8">
       <c r="B27">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C27" t="s">
         <v>58</v>
@@ -1819,12 +1777,12 @@
         <v>1</v>
       </c>
       <c r="H27" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="2:8">
       <c r="B28">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
         <v>60</v>
@@ -1839,21 +1797,21 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="2:8">
       <c r="B29">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C29" t="s">
         <v>62</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="s">
         <v>63</v>
@@ -1865,167 +1823,6 @@
         <v>1</v>
       </c>
       <c r="H29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8">
-      <c r="B30">
-        <v>23</v>
-      </c>
-      <c r="C30" t="s">
-        <v>64</v>
-      </c>
-      <c r="D30">
-        <v>2</v>
-      </c>
-      <c r="E30" t="s">
-        <v>65</v>
-      </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-      <c r="H30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8">
-      <c r="B31">
-        <v>24</v>
-      </c>
-      <c r="C31" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-      <c r="E31" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" t="b">
-        <v>1</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:8">
-      <c r="B32">
-        <v>25</v>
-      </c>
-      <c r="C32" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32">
-        <v>3</v>
-      </c>
-      <c r="E32" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-      <c r="H32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="2:8">
-      <c r="B33">
-        <v>28</v>
-      </c>
-      <c r="C33" t="s">
-        <v>70</v>
-      </c>
-      <c r="D33">
-        <v>2</v>
-      </c>
-      <c r="E33" t="s">
-        <v>71</v>
-      </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33">
-        <v>2</v>
-      </c>
-      <c r="H33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:8">
-      <c r="B34">
-        <v>29</v>
-      </c>
-      <c r="C34" t="s">
-        <v>72</v>
-      </c>
-      <c r="D34">
-        <v>2</v>
-      </c>
-      <c r="E34" t="s">
-        <v>73</v>
-      </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-      <c r="H34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="2:8">
-      <c r="B35">
-        <v>30</v>
-      </c>
-      <c r="C35" t="s">
-        <v>74</v>
-      </c>
-      <c r="D35">
-        <v>2</v>
-      </c>
-      <c r="E35" t="s">
-        <v>75</v>
-      </c>
-      <c r="F35" t="b">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-      <c r="H35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="2:8">
-      <c r="B36">
-        <v>31</v>
-      </c>
-      <c r="C36" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36">
-        <v>2</v>
-      </c>
-      <c r="E36" t="s">
-        <v>77</v>
-      </c>
-      <c r="F36" t="b">
-        <v>0</v>
-      </c>
-      <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36" t="b">
         <v>1</v>
       </c>
     </row>
@@ -2040,7 +1837,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -2051,7 +1848,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27948" windowHeight="11855"/>
+    <workbookView windowWidth="28800" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
   <si>
     <t>#</t>
   </si>
@@ -240,6 +240,12 @@
   </si>
   <si>
     <t>BattlePresetUI</t>
+  </si>
+  <si>
+    <t>宝箱界面</t>
+  </si>
+  <si>
+    <t>TreasureBoxUI</t>
   </si>
 </sst>
 </file>
@@ -1204,12 +1210,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="2" max="2" width="13.1296296296296" customWidth="1"/>
-    <col min="3" max="3" width="25.4444444444444" customWidth="1"/>
-    <col min="4" max="4" width="40.1296296296296" customWidth="1"/>
+    <col min="2" max="2" width="13.1333333333333" customWidth="1"/>
+    <col min="3" max="3" width="25.4416666666667" customWidth="1"/>
+    <col min="4" max="4" width="40.1333333333333" customWidth="1"/>
     <col min="5" max="5" width="23" customWidth="1"/>
     <col min="6" max="6" width="25.5" customWidth="1"/>
     <col min="7" max="7" width="10.5" customWidth="1"/>
@@ -1823,6 +1829,29 @@
         <v>1</v>
       </c>
       <c r="H29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30">
+        <v>32</v>
+      </c>
+      <c r="C30" t="s">
+        <v>64</v>
+      </c>
+      <c r="D30">
+        <v>2</v>
+      </c>
+      <c r="E30" t="s">
+        <v>65</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1837,7 +1866,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -1848,7 +1877,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>#</t>
   </si>
@@ -246,6 +246,12 @@
   </si>
   <si>
     <t>TreasureBoxUI</t>
+  </si>
+  <si>
+    <t>主地图界面</t>
+  </si>
+  <si>
+    <t>OverworldUI</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +1216,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.1333333333333" customWidth="1"/>
@@ -1852,6 +1858,29 @@
         <v>1</v>
       </c>
       <c r="H30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31">
+        <v>33</v>
+      </c>
+      <c r="C31" t="s">
+        <v>66</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31" t="s">
+        <v>67</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="b">
         <v>1</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
   <si>
     <t>#</t>
   </si>
@@ -101,7 +101,7 @@
     <t>返回键触发关闭界面</t>
   </si>
   <si>
-    <t>主界面(顶层)</t>
+    <t>主界面(底层)</t>
   </si>
   <si>
     <t>主菜单</t>
@@ -252,6 +252,12 @@
   </si>
   <si>
     <t>OverworldUI</t>
+  </si>
+  <si>
+    <t>结算界面</t>
+  </si>
+  <si>
+    <t>SettlementUIForm</t>
   </si>
 </sst>
 </file>
@@ -1216,7 +1222,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.1333333333333" customWidth="1"/>
@@ -1881,6 +1887,29 @@
         <v>1</v>
       </c>
       <c r="H31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32">
+        <v>34</v>
+      </c>
+      <c r="C32" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32">
+        <v>2</v>
+      </c>
+      <c r="E32" t="s">
+        <v>69</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>3</v>
+      </c>
+      <c r="H32" t="b">
         <v>1</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
   <si>
     <t>#</t>
   </si>
@@ -258,6 +258,12 @@
   </si>
   <si>
     <t>SettlementUIForm</t>
+  </si>
+  <si>
+    <t>决赛管理界面</t>
+  </si>
+  <si>
+    <t>CharacterBagUI</t>
   </si>
 </sst>
 </file>
@@ -1222,7 +1228,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.1333333333333" customWidth="1"/>
@@ -1910,6 +1916,29 @@
         <v>3</v>
       </c>
       <c r="H32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33">
+        <v>35</v>
+      </c>
+      <c r="C33" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33">
+        <v>2</v>
+      </c>
+      <c r="E33" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33">
+        <v>3</v>
+      </c>
+      <c r="H33" t="b">
         <v>1</v>
       </c>
     </row>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>

--- a/AAAGameData/DataTables/Core/UITable.xlsx
+++ b/AAAGameData/DataTables/Core/UITable.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11925"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
   <si>
     <t>#</t>
   </si>
@@ -264,6 +264,12 @@
   </si>
   <si>
     <t>CharacterBagUI</t>
+  </si>
+  <si>
+    <t>操作指南界面</t>
+  </si>
+  <si>
+    <t>GuideUI</t>
   </si>
 </sst>
 </file>
@@ -1228,7 +1234,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="13.1333333333333" customWidth="1"/>
@@ -1939,6 +1945,29 @@
         <v>1</v>
       </c>
       <c r="H33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" customFormat="1" spans="2:8">
+      <c r="B34">
+        <v>36</v>
+      </c>
+      <c r="C34" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>1</v>
+      </c>
+      <c r="H34" t="b">
         <v>1</v>
       </c>
     </row>
